--- a/파이썬/코딩교실 매크로/3.코딩교실마감/보고서수정/보고서수정.xlsx
+++ b/파이썬/코딩교실 매크로/3.코딩교실마감/보고서수정/보고서수정.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\3.코딩교실마감\보고서수정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53B243B-7144-4244-8D20-BBE9938400B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5110819-0FF6-4BFD-9AAA-0ACBD5E9B480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52830" yWindow="1155" windowWidth="22740" windowHeight="15450" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2970" yWindow="120" windowWidth="21915" windowHeight="15465" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="메인" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="394">
   <si>
     <t>admin ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -227,10 +227,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TT_18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MW_19</t>
   </si>
   <si>
@@ -337,58 +333,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MW_13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MW_14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MW_22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MW_23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MW_31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MW_32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TT_13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TT_14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TT_24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TT_25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TT_26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TT_32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TT_33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>목표월수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -423,594 +367,904 @@
     <t>8회차</t>
   </si>
   <si>
-    <t>노제이</t>
-  </si>
-  <si>
-    <t>김담</t>
-  </si>
-  <si>
-    <t>배도현</t>
-  </si>
-  <si>
-    <t>남은재</t>
-  </si>
-  <si>
-    <t>천윤희</t>
-  </si>
-  <si>
-    <t>오이담</t>
-  </si>
-  <si>
-    <t>김한빈</t>
-  </si>
-  <si>
-    <t>김선후</t>
-  </si>
-  <si>
-    <t>박은우</t>
-  </si>
-  <si>
-    <t>박정연</t>
-  </si>
-  <si>
-    <t>김하윤</t>
-  </si>
-  <si>
-    <t>서민솔</t>
-  </si>
-  <si>
-    <t>김서현</t>
-  </si>
-  <si>
-    <t>오유빈</t>
-  </si>
-  <si>
-    <t>권준휘</t>
-  </si>
-  <si>
-    <t>허유승</t>
-  </si>
-  <si>
-    <t>김이레</t>
-  </si>
-  <si>
-    <t>박재민</t>
-  </si>
-  <si>
-    <t>강재원</t>
-  </si>
-  <si>
-    <t>김태리</t>
-  </si>
-  <si>
-    <t>장하준</t>
-  </si>
-  <si>
-    <t>이다원</t>
-  </si>
-  <si>
-    <t>최율</t>
-  </si>
-  <si>
-    <t>손태율</t>
-  </si>
-  <si>
-    <t>이라엘</t>
-  </si>
-  <si>
-    <t>백시율</t>
-  </si>
-  <si>
-    <t>허지수</t>
-  </si>
-  <si>
-    <t>김제나</t>
-  </si>
-  <si>
-    <t>최혁</t>
-  </si>
-  <si>
-    <t>박현준</t>
-  </si>
-  <si>
-    <t>김우리</t>
-  </si>
-  <si>
-    <t>전태호</t>
-  </si>
-  <si>
-    <t>진지후</t>
-  </si>
-  <si>
-    <t>박든</t>
-  </si>
-  <si>
-    <t>신윤성</t>
-  </si>
-  <si>
-    <t>양성현</t>
-  </si>
-  <si>
-    <t>노채빈</t>
-  </si>
-  <si>
-    <t>함우리</t>
-  </si>
-  <si>
-    <t>김린아</t>
-  </si>
-  <si>
-    <t>김환</t>
-  </si>
-  <si>
-    <t>위제이</t>
-  </si>
-  <si>
-    <t>곽솔</t>
-  </si>
-  <si>
-    <t>곽지후</t>
-  </si>
-  <si>
-    <t>이이은</t>
-  </si>
-  <si>
-    <t>라인우</t>
-  </si>
-  <si>
-    <t>박정민</t>
-  </si>
-  <si>
-    <t>원승우</t>
-  </si>
-  <si>
-    <t>김하리</t>
-  </si>
-  <si>
-    <t>김유건</t>
-  </si>
-  <si>
-    <t>권현민</t>
-  </si>
-  <si>
-    <t>박민석</t>
-  </si>
-  <si>
-    <t>정지호</t>
-  </si>
-  <si>
-    <t>임민성</t>
-  </si>
-  <si>
-    <t>신단</t>
-  </si>
-  <si>
-    <t>임예령</t>
-  </si>
-  <si>
-    <t>배진호</t>
-  </si>
-  <si>
-    <t>하여은</t>
-  </si>
-  <si>
-    <t>박희성</t>
-  </si>
-  <si>
-    <t>장태희</t>
-  </si>
-  <si>
-    <t>방이든</t>
-  </si>
-  <si>
-    <t>신재훈</t>
-  </si>
-  <si>
-    <t>박이한</t>
-  </si>
-  <si>
-    <t>임하음</t>
-  </si>
-  <si>
-    <t>유로한</t>
-  </si>
-  <si>
-    <t>김강준</t>
-  </si>
-  <si>
-    <t>박이안</t>
-  </si>
-  <si>
-    <t>김한별</t>
-  </si>
-  <si>
-    <t>김다예</t>
-  </si>
-  <si>
-    <t>김시하</t>
-  </si>
-  <si>
-    <t>정준원</t>
-  </si>
-  <si>
-    <t>이현서</t>
-  </si>
-  <si>
-    <t>전로하</t>
-  </si>
-  <si>
-    <t>김민건</t>
-  </si>
-  <si>
-    <t>이이루</t>
-  </si>
-  <si>
-    <t>박유담</t>
-  </si>
-  <si>
-    <t>임하민</t>
-  </si>
-  <si>
-    <t>고민호</t>
-  </si>
-  <si>
-    <t>이태겸</t>
-  </si>
-  <si>
-    <t>심지완</t>
-  </si>
-  <si>
-    <t>김신우</t>
-  </si>
-  <si>
-    <t>김준석</t>
-  </si>
-  <si>
-    <t>이해온</t>
-  </si>
-  <si>
-    <t>김준이</t>
-  </si>
-  <si>
-    <t>정도겸</t>
-  </si>
-  <si>
-    <t>이시윤</t>
-  </si>
-  <si>
-    <t>김준원</t>
-  </si>
-  <si>
-    <t>박도원</t>
-  </si>
-  <si>
-    <t>백다희</t>
-  </si>
-  <si>
-    <t>류수혁</t>
-  </si>
-  <si>
-    <t>정라온</t>
-  </si>
-  <si>
-    <t>우건우</t>
-  </si>
-  <si>
-    <t>김주완</t>
-  </si>
-  <si>
-    <t>노다예</t>
-  </si>
-  <si>
-    <t>한동우</t>
-  </si>
-  <si>
-    <t>김주헌</t>
-  </si>
-  <si>
-    <t>염유현</t>
-  </si>
-  <si>
-    <t>정재영</t>
-  </si>
-  <si>
-    <t>강아란</t>
-  </si>
-  <si>
-    <t>소우빈</t>
-  </si>
-  <si>
-    <t>이하엘</t>
-  </si>
-  <si>
-    <t>이민혁</t>
-  </si>
-  <si>
-    <t>염수연</t>
-  </si>
-  <si>
-    <t>정은빈</t>
-  </si>
-  <si>
-    <t>이은재</t>
-  </si>
-  <si>
-    <t>조유민</t>
-  </si>
-  <si>
-    <t>권지민</t>
-  </si>
-  <si>
-    <t>김태건</t>
-  </si>
-  <si>
-    <t>임아준</t>
-  </si>
-  <si>
-    <t>백태우</t>
-  </si>
-  <si>
-    <t>김유호</t>
-  </si>
-  <si>
-    <t>김산</t>
-  </si>
-  <si>
-    <t>강현서</t>
-  </si>
-  <si>
-    <t>임성현</t>
-  </si>
-  <si>
-    <t>유은찬</t>
-  </si>
-  <si>
-    <t>김지웅</t>
-  </si>
-  <si>
-    <t>배아리</t>
-  </si>
-  <si>
-    <t>조서준</t>
-  </si>
-  <si>
-    <t>고진혁</t>
-  </si>
-  <si>
-    <t>정유진</t>
-  </si>
-  <si>
-    <t>김예준</t>
-  </si>
-  <si>
-    <t>박연지</t>
-  </si>
-  <si>
-    <t>곽연우</t>
-  </si>
-  <si>
-    <t>장윤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>송이안</t>
-  </si>
-  <si>
-    <t>이지호</t>
-  </si>
-  <si>
-    <t>손준형</t>
-  </si>
-  <si>
-    <t>최동훈</t>
-  </si>
-  <si>
-    <t>변준</t>
-  </si>
-  <si>
-    <t>이가영</t>
-  </si>
-  <si>
-    <t>이윤후</t>
-  </si>
-  <si>
-    <t>권이든</t>
-  </si>
-  <si>
-    <t>서아라</t>
-  </si>
-  <si>
-    <t>박채민</t>
-  </si>
-  <si>
-    <t>권서진</t>
-  </si>
-  <si>
-    <t>지의준</t>
-  </si>
-  <si>
-    <t>김유빈</t>
-  </si>
-  <si>
-    <t>이하온</t>
-  </si>
-  <si>
-    <t>강정혁</t>
-  </si>
-  <si>
-    <t>이제니</t>
-  </si>
-  <si>
-    <t>류유하</t>
-  </si>
-  <si>
-    <t>백재준</t>
-  </si>
-  <si>
-    <t>정희성</t>
-  </si>
-  <si>
-    <t>최강민</t>
-  </si>
-  <si>
-    <t>김채우</t>
-  </si>
-  <si>
-    <t>최유겸</t>
-  </si>
-  <si>
-    <t>이준기</t>
-  </si>
-  <si>
-    <t>기준우</t>
-  </si>
-  <si>
-    <t>정원우</t>
-  </si>
-  <si>
-    <t>김태오</t>
-  </si>
-  <si>
-    <t>조건호</t>
-  </si>
-  <si>
-    <t>서이안</t>
-  </si>
-  <si>
-    <t>박하온</t>
-  </si>
-  <si>
-    <t>연태호</t>
-  </si>
-  <si>
-    <t>엄윤성</t>
-  </si>
-  <si>
-    <t>송규민</t>
-  </si>
-  <si>
-    <t>김가현</t>
-  </si>
-  <si>
-    <t>박현수</t>
-  </si>
-  <si>
-    <t>김우혁</t>
-  </si>
-  <si>
-    <t>김결</t>
-  </si>
-  <si>
-    <t>장수빈</t>
-  </si>
-  <si>
-    <t>신호윤</t>
-  </si>
-  <si>
-    <t>신인우</t>
-  </si>
-  <si>
-    <t>이지환</t>
-  </si>
-  <si>
-    <t>손태훈</t>
-  </si>
-  <si>
-    <t>박세현</t>
-  </si>
-  <si>
-    <t>강나현</t>
-  </si>
-  <si>
-    <t>이로아</t>
-  </si>
-  <si>
-    <t>김지헌</t>
-  </si>
-  <si>
     <t>김원</t>
   </si>
   <si>
-    <t>정루다</t>
-  </si>
-  <si>
-    <t>고태겸</t>
-  </si>
-  <si>
-    <t>김주원</t>
-  </si>
-  <si>
-    <t>허서현</t>
-  </si>
-  <si>
-    <t>김다연</t>
-  </si>
-  <si>
-    <t>- 자기 소개해봅시다 - 에너지 알아보기 - 코딩이란 무엇일까요? - 엔트리 첫걸음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 인공지능이란 - 엔트리 인공지능 - 작품 확장하기 - 아두이노 연결하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 알고리즘 이해하기 - 순차, 반복, 조건구조 - 알고리즘 사용해보기 - 함지산 친구들</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 전자회로의 기초 - 아두이노란? - 센서와 액추에이터란? - 키트 조립하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 사용할 전자부품 - 적외선 센서 - RGB LED - 피에조 부저</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 무궁화 꽃이 피었습니다 - 기능 확장하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>- 미래를 위한 기술 - 아이디어 구상하기 - 나의 프로젝트 제작하기 - 복습하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>- 학업 성취도 평가 - 나의 프로젝트 발표하기 - 프로젝트 마무리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오서연,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장예솔,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한서준,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오지율,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배지환,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안예서,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정시우,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>손지완,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조승원,4</t>
+    <t>MW_36</t>
+  </si>
+  <si>
+    <t>MW_37</t>
+  </si>
+  <si>
+    <t>MW_38</t>
+  </si>
+  <si>
+    <t>MW_39</t>
+  </si>
+  <si>
+    <t>MW_40</t>
+  </si>
+  <si>
+    <t>TT_36</t>
+  </si>
+  <si>
+    <t>TT_37</t>
+  </si>
+  <si>
+    <t>TT_38</t>
+  </si>
+  <si>
+    <t>TT_39</t>
+  </si>
+  <si>
+    <t>TT_40</t>
+  </si>
+  <si>
+    <t>- 자기 소개해봅시다 - 멸종위기동물 알아보기 - 메타버스와 VR/AR - 딜라잇텍스 첫걸음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 멸종위기보호 동물원 - 알고리즘 이해하기 -순차, 반복, 조건구조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 생활 속 물리 이야기 - 물리 속성 실험실 - 갈릴레이 실험실 - 자동차 장애물 추돌 - 자동차 레이싱 게임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 멸종위기동물 조사하기 - 서식지 구성하기 - 기능 확장하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- VR 롤러코스터 - VR 동물원 꾸미기 - VR 열기구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 팅커캐드 접속하기 - 3D 모델링하기 - 머지큐브 알아보기 - AR 멸종위기동물 설명서 - AR 서식지 구현하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 멸종위기동물 보호 - 멸종위기동물보호 콘텐츠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MW_37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MW_38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TT_29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TT_36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TT_37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강시진</t>
+  </si>
+  <si>
+    <t>김주영</t>
+  </si>
+  <si>
+    <t>박가민</t>
+  </si>
+  <si>
+    <t>박우빈</t>
+  </si>
+  <si>
+    <t>송도윤</t>
+  </si>
+  <si>
+    <t>이아준</t>
+  </si>
+  <si>
+    <t>이영웅</t>
+  </si>
+  <si>
+    <t>김단아</t>
+  </si>
+  <si>
+    <t>김지예</t>
+  </si>
+  <si>
+    <t>김한솔</t>
+  </si>
+  <si>
+    <t>이주안</t>
+  </si>
+  <si>
+    <t>박시영</t>
+  </si>
+  <si>
+    <t>지정우</t>
+  </si>
+  <si>
+    <t>강로윤</t>
+  </si>
+  <si>
+    <t>천예랑</t>
+  </si>
+  <si>
+    <t>공윤오</t>
+  </si>
+  <si>
+    <t>김소망</t>
+  </si>
+  <si>
+    <t>최찬우</t>
+  </si>
+  <si>
+    <t>한혜원</t>
+  </si>
+  <si>
+    <t>길선우</t>
+  </si>
+  <si>
+    <t>김시진</t>
+  </si>
+  <si>
+    <t>이준석</t>
+  </si>
+  <si>
+    <t>이하빈</t>
+  </si>
+  <si>
+    <t>임규원</t>
+  </si>
+  <si>
+    <t>정은설</t>
+  </si>
+  <si>
+    <t>김도담</t>
+  </si>
+  <si>
+    <t>김정후</t>
+  </si>
+  <si>
+    <t>서여준</t>
+  </si>
+  <si>
+    <t>유강민</t>
+  </si>
+  <si>
+    <t>한희찬</t>
+  </si>
+  <si>
+    <t>이진아</t>
+  </si>
+  <si>
+    <t>홍서율</t>
+  </si>
+  <si>
+    <t>김이현</t>
+  </si>
+  <si>
+    <t>김지윤</t>
+  </si>
+  <si>
+    <t>남은수</t>
+  </si>
+  <si>
+    <t>최정현</t>
+  </si>
+  <si>
+    <t>최주성</t>
+  </si>
+  <si>
+    <t>김시온</t>
+  </si>
+  <si>
+    <t>김주혁</t>
+  </si>
+  <si>
+    <t>박혜림</t>
+  </si>
+  <si>
+    <t>신서은</t>
+  </si>
+  <si>
+    <t>안태규</t>
+  </si>
+  <si>
+    <t>이로이</t>
+  </si>
+  <si>
+    <t>이로하</t>
+  </si>
+  <si>
+    <t>이해성</t>
+  </si>
+  <si>
+    <t>권아리</t>
+  </si>
+  <si>
+    <t>조가온</t>
+  </si>
+  <si>
+    <t>문강</t>
+  </si>
+  <si>
+    <t>유재율</t>
+  </si>
+  <si>
+    <t>이도경</t>
+  </si>
+  <si>
+    <t>최설</t>
+  </si>
+  <si>
+    <t>조하루</t>
+  </si>
+  <si>
+    <t>서솔</t>
+  </si>
+  <si>
+    <t>양이솔</t>
+  </si>
+  <si>
+    <t>김서영</t>
+  </si>
+  <si>
+    <t>라희윤</t>
+  </si>
+  <si>
+    <t>박하영</t>
+  </si>
+  <si>
+    <t>송예준</t>
+  </si>
+  <si>
+    <t>하이현</t>
+  </si>
+  <si>
+    <t>강도한</t>
+  </si>
+  <si>
+    <t>박세윤</t>
+  </si>
+  <si>
+    <t>채가람</t>
+  </si>
+  <si>
+    <t>신예온</t>
+  </si>
+  <si>
+    <t>유모아</t>
+  </si>
+  <si>
+    <t>이은율</t>
+  </si>
+  <si>
+    <t>이인우</t>
+  </si>
+  <si>
+    <t>최세현</t>
+  </si>
+  <si>
+    <t>원연준</t>
+  </si>
+  <si>
+    <t>임건율</t>
+  </si>
+  <si>
+    <t>최희진</t>
+  </si>
+  <si>
+    <t>석이서</t>
+  </si>
+  <si>
+    <t>박다정</t>
+  </si>
+  <si>
+    <t>서하니</t>
+  </si>
+  <si>
+    <t>안성하</t>
+  </si>
+  <si>
+    <t>이해솔</t>
+  </si>
+  <si>
+    <t>김찬율</t>
+  </si>
+  <si>
+    <t>김시준</t>
+  </si>
+  <si>
+    <t>송지온</t>
+  </si>
+  <si>
+    <t>이지은</t>
+  </si>
+  <si>
+    <t>장이랑</t>
+  </si>
+  <si>
+    <t>김여원</t>
+  </si>
+  <si>
+    <t>이민겸</t>
+  </si>
+  <si>
+    <t>최윤호</t>
+  </si>
+  <si>
+    <t>현정윤</t>
+  </si>
+  <si>
+    <t>성동준</t>
+  </si>
+  <si>
+    <t>송정인</t>
+  </si>
+  <si>
+    <t>위도하</t>
+  </si>
+  <si>
+    <t>김동연</t>
+  </si>
+  <si>
+    <t>전재연</t>
+  </si>
+  <si>
+    <t>박다빈</t>
+  </si>
+  <si>
+    <t>이다해</t>
+  </si>
+  <si>
+    <t>임지유</t>
+  </si>
+  <si>
+    <t>김유솔</t>
+  </si>
+  <si>
+    <t>이인호</t>
+  </si>
+  <si>
+    <t>정이환</t>
+  </si>
+  <si>
+    <t>허소예</t>
+  </si>
+  <si>
+    <t>김하늘</t>
+  </si>
+  <si>
+    <t>문아정</t>
+  </si>
+  <si>
+    <t>이혁</t>
+  </si>
+  <si>
+    <t>최성훈</t>
+  </si>
+  <si>
+    <t>김강인</t>
+  </si>
+  <si>
+    <t>박동규</t>
+  </si>
+  <si>
+    <t>황수안</t>
+  </si>
+  <si>
+    <t>신성민</t>
+  </si>
+  <si>
+    <t>여로하</t>
+  </si>
+  <si>
+    <t>장승유</t>
+  </si>
+  <si>
+    <t>정서안</t>
+  </si>
+  <si>
+    <t>지예린</t>
+  </si>
+  <si>
+    <t>최혜린</t>
+  </si>
+  <si>
+    <t>홍하경</t>
+  </si>
+  <si>
+    <t>박유주</t>
+  </si>
+  <si>
+    <t>정서원</t>
+  </si>
+  <si>
+    <t>차한</t>
+  </si>
+  <si>
+    <t>홍상현</t>
+  </si>
+  <si>
+    <t>김소현</t>
+  </si>
+  <si>
+    <t>최소영</t>
+  </si>
+  <si>
+    <t>홍미나</t>
+  </si>
+  <si>
+    <t>김강빈</t>
+  </si>
+  <si>
+    <t>김채영</t>
+  </si>
+  <si>
+    <t>장윤지</t>
+  </si>
+  <si>
+    <t>최태온</t>
+  </si>
+  <si>
+    <t>김세인</t>
+  </si>
+  <si>
+    <t>박민희</t>
+  </si>
+  <si>
+    <t>신태웅</t>
+  </si>
+  <si>
+    <t>채리사</t>
+  </si>
+  <si>
+    <t>김나예</t>
+  </si>
+  <si>
+    <t>신민</t>
+  </si>
+  <si>
+    <t>오세아</t>
+  </si>
+  <si>
+    <t>황겸</t>
+  </si>
+  <si>
+    <t>박진</t>
+  </si>
+  <si>
+    <t>서루다</t>
+  </si>
+  <si>
+    <t>선지웅</t>
+  </si>
+  <si>
+    <t>안다솜</t>
+  </si>
+  <si>
+    <t>이시준</t>
+  </si>
+  <si>
+    <t>김준형</t>
+  </si>
+  <si>
+    <t>윤희준</t>
+  </si>
+  <si>
+    <t>조영준</t>
+  </si>
+  <si>
+    <t>조채우</t>
+  </si>
+  <si>
+    <t>차정원</t>
+  </si>
+  <si>
+    <t>김해온</t>
+  </si>
+  <si>
+    <t>박담희</t>
+  </si>
+  <si>
+    <t>이정원</t>
+  </si>
+  <si>
+    <t>허준환</t>
+  </si>
+  <si>
+    <t>김하온</t>
+  </si>
+  <si>
+    <t>변서연</t>
+  </si>
+  <si>
+    <t>유루이</t>
+  </si>
+  <si>
+    <t>송태양</t>
+  </si>
+  <si>
+    <t>김다나</t>
+  </si>
+  <si>
+    <t>김민제</t>
+  </si>
+  <si>
+    <t>민우재</t>
+  </si>
+  <si>
+    <t>서정아</t>
+  </si>
+  <si>
+    <t>한재하</t>
+  </si>
+  <si>
+    <t>문민수</t>
+  </si>
+  <si>
+    <t>배서우</t>
+  </si>
+  <si>
+    <t>이정안</t>
+  </si>
+  <si>
+    <t>임유현</t>
+  </si>
+  <si>
+    <t>홍도율</t>
+  </si>
+  <si>
+    <t>류재윤</t>
+  </si>
+  <si>
+    <t>박신우</t>
+  </si>
+  <si>
+    <t>오여진</t>
+  </si>
+  <si>
+    <t>이가온</t>
+  </si>
+  <si>
+    <t>조동건</t>
+  </si>
+  <si>
+    <t>손승민</t>
+  </si>
+  <si>
+    <t>진태윤</t>
+  </si>
+  <si>
+    <t>최준혁</t>
+  </si>
+  <si>
+    <t>양다연</t>
+  </si>
+  <si>
+    <t>이민후</t>
+  </si>
+  <si>
+    <t>이준호</t>
+  </si>
+  <si>
+    <t>한한나</t>
+  </si>
+  <si>
+    <t>이혜주</t>
+  </si>
+  <si>
+    <t>권지오</t>
+  </si>
+  <si>
+    <t>이윤건</t>
+  </si>
+  <si>
+    <t>박경민</t>
+  </si>
+  <si>
+    <t>최도준</t>
+  </si>
+  <si>
+    <t>김민석</t>
+  </si>
+  <si>
+    <t>송윤성</t>
+  </si>
+  <si>
+    <t>임세린</t>
+  </si>
+  <si>
+    <t>전도건</t>
+  </si>
+  <si>
+    <t>김세빈</t>
+  </si>
+  <si>
+    <t>김윤채</t>
+  </si>
+  <si>
+    <t>서건후</t>
+  </si>
+  <si>
+    <t>장동하</t>
+  </si>
+  <si>
+    <t>라윤서</t>
+  </si>
+  <si>
+    <t>문은율</t>
+  </si>
+  <si>
+    <t>박다온</t>
+  </si>
+  <si>
+    <t>서지유</t>
+  </si>
+  <si>
+    <t>서한울</t>
+  </si>
+  <si>
+    <t>이수하</t>
+  </si>
+  <si>
+    <t>이유성</t>
+  </si>
+  <si>
+    <t>주재민</t>
+  </si>
+  <si>
+    <t>고규빈</t>
+  </si>
+  <si>
+    <t>서규림</t>
+  </si>
+  <si>
+    <t>정은성</t>
+  </si>
+  <si>
+    <t>이주성</t>
+  </si>
+  <si>
+    <t>배승유</t>
+  </si>
+  <si>
+    <t>조도경</t>
+  </si>
+  <si>
+    <t>조유하</t>
+  </si>
+  <si>
+    <t>강보경</t>
+  </si>
+  <si>
+    <t>윤환희</t>
+  </si>
+  <si>
+    <t>국보민</t>
+  </si>
+  <si>
+    <t>이은유</t>
+  </si>
+  <si>
+    <t>박나경</t>
+  </si>
+  <si>
+    <t>위승빈</t>
+  </si>
+  <si>
+    <t>박지용</t>
+  </si>
+  <si>
+    <t>박태환</t>
+  </si>
+  <si>
+    <t>이다영</t>
+  </si>
+  <si>
+    <t>진고은</t>
+  </si>
+  <si>
+    <t>양채원</t>
+  </si>
+  <si>
+    <t>조민준</t>
+  </si>
+  <si>
+    <t>정진우</t>
+  </si>
+  <si>
+    <t>조로빈</t>
+  </si>
+  <si>
+    <t>박채령</t>
+  </si>
+  <si>
+    <t>이주연</t>
+  </si>
+  <si>
+    <t>최태유</t>
+  </si>
+  <si>
+    <t>고유안</t>
+  </si>
+  <si>
+    <t>김다현</t>
+  </si>
+  <si>
+    <t>차태희</t>
+  </si>
+  <si>
+    <t>강신</t>
+  </si>
+  <si>
+    <t>박가은</t>
+  </si>
+  <si>
+    <t>임규린</t>
+  </si>
+  <si>
+    <t>류재희</t>
+  </si>
+  <si>
+    <t>박하담</t>
+  </si>
+  <si>
+    <t>안이삭</t>
+  </si>
+  <si>
+    <t>이시진</t>
+  </si>
+  <si>
+    <t>하은규</t>
+  </si>
+  <si>
+    <t>김소을</t>
+  </si>
+  <si>
+    <t>윤라현</t>
+  </si>
+  <si>
+    <t>김은수</t>
+  </si>
+  <si>
+    <t>최리온</t>
+  </si>
+  <si>
+    <t>김지율</t>
+  </si>
+  <si>
+    <t>김지훈</t>
+  </si>
+  <si>
+    <t>류혜준</t>
+  </si>
+  <si>
+    <t>박찬</t>
+  </si>
+  <si>
+    <t>이의빈</t>
+  </si>
+  <si>
+    <t>강서이</t>
+  </si>
+  <si>
+    <t>김한울</t>
+  </si>
+  <si>
+    <t>조진혁</t>
+  </si>
+  <si>
+    <t>최예훈</t>
+  </si>
+  <si>
+    <t>홍이현</t>
+  </si>
+  <si>
+    <t>고예봄</t>
+  </si>
+  <si>
+    <t>최은혜</t>
+  </si>
+  <si>
+    <t>김유환</t>
+  </si>
+  <si>
+    <t>류예담</t>
+  </si>
+  <si>
+    <t>이민하</t>
+  </si>
+  <si>
+    <t>신현</t>
+  </si>
+  <si>
+    <t>조리우</t>
+  </si>
+  <si>
+    <t>김미소</t>
+  </si>
+  <si>
+    <t>최은비</t>
+  </si>
+  <si>
+    <t>김서온</t>
+  </si>
+  <si>
+    <t>정시원</t>
+  </si>
+  <si>
+    <t>이하겸</t>
+  </si>
+  <si>
+    <t>신동하</t>
+  </si>
+  <si>
+    <t>신승재</t>
+  </si>
+  <si>
+    <t>김재이</t>
+  </si>
+  <si>
+    <t>박윤하</t>
+  </si>
+  <si>
+    <t>이서인</t>
+  </si>
+  <si>
+    <t>이하람</t>
+  </si>
+  <si>
+    <t>김재인</t>
+  </si>
+  <si>
+    <t>김혜리</t>
+  </si>
+  <si>
+    <t>문효준</t>
+  </si>
+  <si>
+    <t>이지한</t>
+  </si>
+  <si>
+    <t>이하진</t>
+  </si>
+  <si>
+    <t>임보미</t>
+  </si>
+  <si>
+    <t>정우현</t>
+  </si>
+  <si>
+    <t>신재민,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조성원,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>천영민,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>류호정,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이인성,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성지민,5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1018,7 +1272,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1076,14 +1330,6 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -1191,7 +1437,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1267,11 +1513,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1623,10 +1875,10 @@
         <v>9</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="S1" s="20" t="s">
-        <v>288</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="18" thickTop="1" thickBot="1">
@@ -1643,10 +1895,10 @@
         <v>11</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>290</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="17.25" thickBot="1">
@@ -1663,10 +1915,10 @@
         <v>3</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>289</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="17.25" thickBot="1">
@@ -1683,10 +1935,10 @@
         <v>4</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>291</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="17.25" thickBot="1">
@@ -1703,10 +1955,10 @@
         <v>54</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>292</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="17.25" thickBot="1">
@@ -1720,13 +1972,13 @@
         <v>15</v>
       </c>
       <c r="Q6" s="2">
-        <v>202506</v>
+        <v>202509</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>293</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="17.25" thickBot="1">
@@ -1740,13 +1992,13 @@
         <v>51</v>
       </c>
       <c r="Q7" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>294</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="17.25" thickBot="1">
@@ -1760,13 +2012,13 @@
         <v>52</v>
       </c>
       <c r="Q8" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>295</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="17.25" thickBot="1">
@@ -1777,10 +2029,10 @@
       <c r="G9" s="2"/>
       <c r="K9" s="4"/>
       <c r="P9" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="Q9" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="17.25" thickBot="1">
@@ -1791,10 +2043,10 @@
       <c r="G10" s="2"/>
       <c r="K10" s="4"/>
       <c r="P10" s="2" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="Q10" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="17.25" thickBot="1">
@@ -2154,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBA0246-B961-4C43-83D8-E960CF2453EE}">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -2204,373 +2456,420 @@
       <c r="A9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>31</v>
+      <c r="B12" s="19" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>93</v>
+      <c r="B13" s="19" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>94</v>
+      <c r="B14" s="19" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>61</v>
+      <c r="B15" s="19" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>62</v>
+      <c r="B16" s="19" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>95</v>
+      <c r="B17" s="19" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>96</v>
+      <c r="B18" s="19" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="19" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" s="19" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="19" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" s="19" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:1">
       <c r="A36" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="19" t="s">
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="19" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="19" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="19" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" s="19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="19" t="s">
+    <row r="47" spans="1:1">
+      <c r="A47" s="19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="19" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="19" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>100</v>
+        <v>42</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>101</v>
+        <v>43</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>102</v>
+        <v>44</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>103</v>
+        <v>45</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="19" t="s">
-        <v>73</v>
+        <v>46</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
-        <v>74</v>
+        <v>47</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="19" t="s">
-        <v>75</v>
+        <v>48</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="19" t="s">
-        <v>76</v>
+        <v>49</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="19" t="s">
-        <v>77</v>
+        <v>50</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="19" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="19" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="19" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="19" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="19" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="19" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="19" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="19" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="19" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2581,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{677ADA0E-C988-422F-B5F6-5CF6B4D028AF}">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -2596,6 +2895,9 @@
       <c r="A2" s="19" t="s">
         <v>17</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="19" t="s">
@@ -2611,9 +2913,6 @@
       <c r="A5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>296</v>
-      </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="19" t="s">
@@ -2624,22 +2923,19 @@
       <c r="A7" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>297</v>
-      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="19" t="s">
         <v>23</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>302</v>
-      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="19" t="s">
@@ -2650,6 +2946,9 @@
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
+      <c r="B11" s="2" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="19" t="s">
@@ -2670,9 +2969,6 @@
       <c r="A15" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>303</v>
-      </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="19" t="s">
@@ -2683,9 +2979,6 @@
       <c r="A17" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>298</v>
-      </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="19" t="s">
@@ -2694,274 +2987,321 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="19" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" s="19" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="19" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" s="19" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:1">
       <c r="A36" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="19" t="s">
+    <row r="42" spans="1:1">
+      <c r="A42" s="19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="19" t="s">
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="19" t="s">
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="19" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" s="19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="19" t="s">
+    <row r="47" spans="1:1">
+      <c r="A47" s="19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="19" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="19" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="19" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="19" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>300</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="19" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="19" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="19" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="19" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="19" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="19" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="19" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="19" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="19" t="s">
+      <c r="B70" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="19" t="s">
+    <row r="72" spans="1:2">
+      <c r="A72" s="19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="19" t="s">
+    <row r="73" spans="1:2">
+      <c r="A73" s="19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="19" t="s">
+    <row r="74" spans="1:2">
+      <c r="A74" s="19" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="19" t="s">
+    <row r="75" spans="1:2">
+      <c r="A75" s="19" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="19" t="s">
-        <v>89</v>
+    <row r="76" spans="1:2">
+      <c r="A76" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="19" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2972,890 +3312,1067 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0500CDB6-F6D5-4458-8137-AF5312222B51}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:80" ht="17.25" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="19" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="19" t="s">
+      <c r="C1" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A8" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A9" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A10" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="22" t="s">
+      <c r="K1" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="T1" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="U1" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="V1" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="W1" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="X1" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y1" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z1" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA1" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB1" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC1" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD1" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE1" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF1" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG1" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH1" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI1" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ1" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK1" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL1" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM1" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN1" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO1" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP1" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AQ1" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR1" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS1" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AU1" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AV1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="AW1" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="AX1" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AY1" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AZ1" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="BA1" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="BB1" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="BC1" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="BD1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="BE1" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="BF1" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="BG1" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="BH1" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="BI1" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ1" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="BK1" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL1" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="BM1" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="BN1" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="BO1" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP1" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="BQ1" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BR1" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS1" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="BT1" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="BU1" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="BV1" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="BW1" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="BX1" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="BY1" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BZ1" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA1" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="CB1" s="19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80" ht="18" thickTop="1" thickBot="1">
+      <c r="F2" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="G2" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="H2" s="25" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A11" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="I2" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="J2" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="L2" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="M2" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q2" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="S2" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="T2" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="U2" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="V2" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="W2" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="X2" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y2" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z2" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="AA2" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB2" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD2" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="AE2" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="AF2" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="AG2" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="AH2" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="AI2" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="AJ2" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="AX2" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="AY2" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="AZ2" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="BA2" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="BB2" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="BC2" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="BD2" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="BE2" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="BF2" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="BG2" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="BH2" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="BI2" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="BJ2" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="BK2" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="BL2" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="BM2" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="BN2" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="BO2" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="BP2" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="BQ2" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="BR2" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="BS2" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="BT2" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="BU2" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="BV2" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="BW2" s="22" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80" ht="17.25" thickBot="1">
+      <c r="L3" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="M3" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="O3" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="P3" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q3" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="V3" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="W3" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="X3" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y3" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA3" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB3" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE3" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="AF3" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="AG3" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="AH3" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="AI3" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="AJ3" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX3" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="AY3" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ3" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="BA3" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="BB3" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="BC3" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="BD3" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="BE3" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="BF3" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="BH3" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="BK3" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="BL3" s="22" t="s">
+        <v>326</v>
+      </c>
+      <c r="BM3" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="BN3" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="BO3" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="BS3" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="BT3" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="BU3" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="BV3" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="BW3" s="22" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80" ht="17.25" thickBot="1">
+      <c r="L4" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="M4" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="N4" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="O4" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="P4" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q4" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="V4" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="W4" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="X4" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y4" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z4" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA4" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB4" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE4" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="AF4" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="AG4" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="AH4" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI4" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="AJ4" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="AX4" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="AY4" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="AZ4" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="BA4" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="BB4" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="BC4" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="BD4" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="BE4" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="BF4" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="BK4" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="BL4" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="BM4" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="BN4" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="BO4" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="BS4" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="BT4" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="BU4" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="BV4" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="BW4" s="22" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80" ht="17.25" thickBot="1">
+      <c r="L5" s="22" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="21" t="s">
+      <c r="M5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="N5" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="O5" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="P5" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q5" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="V5" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="W5" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="X5" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y5" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z5" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA5" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE5" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="AF5" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG5" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="AH5" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="AI5" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="AJ5" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="AX5" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="AY5" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="AZ5" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="BA5" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="BB5" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="BC5" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="BD5" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="BE5" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="BL5" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="BM5" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="BN5" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="BO5" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="BS5" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="BT5" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="BU5" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="BV5" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="BW5" s="22" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80" ht="17.25" thickBot="1">
+      <c r="L6" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="M6" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="N6" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="O6" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="P6" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q6" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="W6" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="X6" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y6" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z6" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA6" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE6" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="AF6" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="AG6" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH6" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI6" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ6" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="AX6" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="AY6" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="AZ6" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="BA6" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="BB6" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="BC6" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="BD6" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="BE6" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="BL6" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="BM6" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="BN6" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="BO6" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="BS6" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="BT6" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="BU6" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="BV6" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="BW6" s="22" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80" ht="17.25" thickBot="1">
+      <c r="L7" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="M7" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="N7" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="O7" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="P7" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q7" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="W7" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="X7" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y7" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z7" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA7" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="AE7" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="AF7" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="AG7" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="AH7" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI7" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="AJ7" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="AX7" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="AY7" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="AZ7" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="BA7" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="BB7" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="BC7" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="BD7" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="BE7" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="BL7" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="BM7" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="BN7" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="BO7" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="BS7" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="BT7" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="BU7" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="BV7" s="22" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80" ht="17.25" thickBot="1">
+      <c r="L8" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A16" s="19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A17" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="F17" s="22" t="s">
+      <c r="M8" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="G17" s="23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A18" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="G18" s="23" t="s">
+      <c r="N8" s="23" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A19" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A20" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="21" t="s">
+      <c r="O8" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="C20" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A21" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="22" t="s">
+      <c r="P8" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="D21" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="17.25" thickBot="1">
-      <c r="A25" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A26" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="D26" s="22" t="s">
+      <c r="Q8" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A27" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A28" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F28" s="22" t="s">
+      <c r="W8" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="H28" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A29" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="F29" s="22" t="s">
+      <c r="X8" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="G29" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="18" thickTop="1" thickBot="1">
-      <c r="A30" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="F30" s="22" t="s">
+      <c r="Y8" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="G30" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="H30" s="23" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A35" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A36" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="F36" s="22" t="s">
+      <c r="Z8" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="G36" s="23" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A43" s="19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A44" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E44" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="F44" s="23" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A45" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="21" t="s">
+      <c r="AA8" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="C45" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="F45" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="G45" s="23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A46" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="G46" s="23" t="s">
+      <c r="AE8" s="23" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A47" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="G47" s="23" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A53" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B53" s="26" t="s">
+      <c r="AF8" s="23" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A54" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="G54" s="25" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A55" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B55" s="21" t="s">
+      <c r="AG8" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="C55" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="G55" s="23" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A56" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="22" t="s">
+      <c r="AH8" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="D56" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="F56" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A57" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="D57" s="22" t="s">
+      <c r="AI8" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="E57" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="F57" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="G57" s="23" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A58" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="C58" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="D58" s="22" t="s">
+      <c r="AJ8" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="E58" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="F58" s="22" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="19" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A61" s="19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A62" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="C62" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="D62" s="22" t="s">
-        <v>262</v>
-      </c>
-      <c r="E62" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F62" s="23" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A63" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B63" s="21" t="s">
+      <c r="AX8" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="C63" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="E63" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="F63" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="G63" s="23" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A64" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B64" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="C64" s="22" t="s">
+      <c r="AY8" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="D64" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="E64" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="F64" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="G64" s="23" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A65" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B65" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="C65" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="D65" s="22" t="s">
+      <c r="AZ8" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="E65" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="F65" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="G65" s="23" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="18" thickTop="1" thickBot="1">
-      <c r="A66" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B66" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="C66" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="E66" s="22" t="s">
+      <c r="BA8" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="F66" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="G66" s="23" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="19" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="19" t="s">
-        <v>89</v>
-      </c>
-    </row>
+      <c r="BB8" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="BC8" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="BD8" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="BE8" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="BL8" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="BM8" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="BN8" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="BO8" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="BS8" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="BT8" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="BU8" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="BV8" s="23" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80" ht="17.25" thickTop="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/파이썬/코딩교실 매크로/3.코딩교실마감/보고서수정/보고서수정.xlsx
+++ b/파이썬/코딩교실 매크로/3.코딩교실마감/보고서수정/보고서수정.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\3.코딩교실마감\보고서수정\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\3.코딩교실마감\보고서수정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53B243B-7144-4244-8D20-BBE9938400B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290FB25D-7FAE-468C-8043-8B8061DE2B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52830" yWindow="1155" windowWidth="22740" windowHeight="15450" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="메인" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="306">
   <si>
     <t>admin ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1011,6 +1011,10 @@
   </si>
   <si>
     <t>조승원,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>z</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1590,30 +1594,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S53"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="93" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" style="2" customWidth="1"/>
     <col min="4" max="4" width="9" style="2"/>
-    <col min="5" max="5" width="10.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.375" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" style="2" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="20.5" style="5" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="7.125" style="2" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="7.09765625" style="2" hidden="1" customWidth="1"/>
     <col min="9" max="10" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="13.3984375" style="2" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="2" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" style="2" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="7.09765625" style="2" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="0" style="2" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="9" style="2"/>
-    <col min="16" max="16" width="18.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="57.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="57.09765625" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9" style="2"/>
-    <col min="19" max="19" width="87.25" style="5" customWidth="1"/>
+    <col min="19" max="19" width="87.19921875" style="5" customWidth="1"/>
     <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" thickBot="1">
+    <row r="1" spans="1:19" ht="18" thickBot="1">
       <c r="B1" s="5"/>
       <c r="L1" s="5"/>
       <c r="P1" s="2" t="s">
@@ -1629,7 +1633,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="18" thickTop="1" thickBot="1">
+    <row r="2" spans="1:19" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A2" s="15"/>
       <c r="B2" s="18"/>
       <c r="C2" s="8"/>
@@ -1649,7 +1653,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="17.25" thickBot="1">
+    <row r="3" spans="1:19" ht="18" thickBot="1">
       <c r="A3" s="11"/>
       <c r="B3" s="16"/>
       <c r="C3" s="6"/>
@@ -1669,7 +1673,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="17.25" thickBot="1">
+    <row r="4" spans="1:19" ht="18" thickBot="1">
       <c r="A4" s="11"/>
       <c r="B4" s="17"/>
       <c r="C4" s="6"/>
@@ -1689,7 +1693,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="17.25" thickBot="1">
+    <row r="5" spans="1:19" ht="18" thickBot="1">
       <c r="A5" s="11"/>
       <c r="B5" s="16"/>
       <c r="C5" s="6"/>
@@ -1709,7 +1713,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="17.25" thickBot="1">
+    <row r="6" spans="1:19" ht="18" thickBot="1">
       <c r="A6" s="11"/>
       <c r="B6" s="17"/>
       <c r="C6" s="6"/>
@@ -1720,7 +1724,7 @@
         <v>15</v>
       </c>
       <c r="Q6" s="2">
-        <v>202506</v>
+        <v>202509</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>111</v>
@@ -1729,7 +1733,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.25" thickBot="1">
+    <row r="7" spans="1:19" ht="18" thickBot="1">
       <c r="A7" s="11"/>
       <c r="B7" s="16"/>
       <c r="C7" s="6"/>
@@ -1740,7 +1744,7 @@
         <v>51</v>
       </c>
       <c r="Q7" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>112</v>
@@ -1749,7 +1753,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="17.25" thickBot="1">
+    <row r="8" spans="1:19" ht="18" thickBot="1">
       <c r="A8" s="11"/>
       <c r="B8" s="17"/>
       <c r="C8" s="6"/>
@@ -1760,7 +1764,7 @@
         <v>52</v>
       </c>
       <c r="Q8" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>113</v>
@@ -1769,7 +1773,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.25" thickBot="1">
+    <row r="9" spans="1:19" ht="18" thickBot="1">
       <c r="A9" s="11"/>
       <c r="B9" s="16"/>
       <c r="C9" s="7"/>
@@ -1780,10 +1784,10 @@
         <v>104</v>
       </c>
       <c r="Q9" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="17.25" thickBot="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="18" thickBot="1">
       <c r="A10" s="11"/>
       <c r="B10" s="17"/>
       <c r="C10" s="6"/>
@@ -1794,10 +1798,10 @@
         <v>105</v>
       </c>
       <c r="Q10" s="2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="17.25" thickBot="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="18" thickBot="1">
       <c r="A11" s="11"/>
       <c r="B11" s="16"/>
       <c r="C11" s="6"/>
@@ -1805,7 +1809,7 @@
       <c r="G11" s="2"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:19" ht="17.25" thickBot="1">
+    <row r="12" spans="1:19" ht="18" thickBot="1">
       <c r="A12" s="11"/>
       <c r="B12" s="17"/>
       <c r="C12" s="6"/>
@@ -1813,7 +1817,7 @@
       <c r="G12" s="2"/>
       <c r="K12" s="4"/>
     </row>
-    <row r="13" spans="1:19" ht="17.25" thickBot="1">
+    <row r="13" spans="1:19" ht="18" thickBot="1">
       <c r="A13" s="11"/>
       <c r="B13" s="16"/>
       <c r="C13" s="6"/>
@@ -1821,15 +1825,18 @@
       <c r="G13" s="2"/>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:19" ht="17.25" thickBot="1">
+    <row r="14" spans="1:19" ht="18" thickBot="1">
       <c r="A14" s="11"/>
       <c r="B14" s="17"/>
       <c r="C14" s="6"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2"/>
       <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:19" ht="17.25" thickBot="1">
+      <c r="Q14" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="18" thickBot="1">
       <c r="A15" s="11"/>
       <c r="B15" s="16"/>
       <c r="C15" s="6"/>
@@ -1837,7 +1844,7 @@
       <c r="G15" s="2"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="1:19" ht="17.25" thickBot="1">
+    <row r="16" spans="1:19" ht="18" thickBot="1">
       <c r="A16" s="11"/>
       <c r="B16" s="17"/>
       <c r="C16" s="6"/>
@@ -1845,7 +1852,7 @@
       <c r="G16" s="2"/>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" spans="1:17" ht="18" thickTop="1" thickBot="1">
+    <row r="17" spans="1:17" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A17" s="11"/>
       <c r="B17" s="16"/>
       <c r="C17" s="8"/>
@@ -1859,7 +1866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.25" thickBot="1">
+    <row r="18" spans="1:17" ht="18" thickBot="1">
       <c r="A18" s="11"/>
       <c r="B18" s="17"/>
       <c r="C18" s="6"/>
@@ -1870,7 +1877,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.25" thickBot="1">
+    <row r="19" spans="1:17" ht="18" thickBot="1">
       <c r="A19" s="11"/>
       <c r="B19" s="16"/>
       <c r="C19" s="6"/>
@@ -1884,7 +1891,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.25" thickBot="1">
+    <row r="20" spans="1:17" ht="18" thickBot="1">
       <c r="A20" s="10"/>
       <c r="B20" s="18"/>
       <c r="C20" s="6"/>
@@ -1895,7 +1902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.25" thickBot="1">
+    <row r="21" spans="1:17" ht="18" thickBot="1">
       <c r="A21" s="11"/>
       <c r="B21" s="16"/>
       <c r="C21" s="6"/>
@@ -1909,7 +1916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="17.25" thickBot="1">
+    <row r="22" spans="1:17" ht="18" thickBot="1">
       <c r="A22" s="12"/>
       <c r="B22" s="17"/>
       <c r="C22" s="6"/>
@@ -1920,7 +1927,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.25" thickBot="1">
+    <row r="23" spans="1:17" ht="18" thickBot="1">
       <c r="A23" s="11"/>
       <c r="B23" s="16"/>
       <c r="C23" s="13"/>
@@ -1928,7 +1935,7 @@
       <c r="G23" s="2"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:17" ht="17.25" thickBot="1">
+    <row r="24" spans="1:17" ht="18" thickBot="1">
       <c r="A24" s="12"/>
       <c r="B24" s="17"/>
       <c r="C24" s="7"/>
@@ -1936,7 +1943,7 @@
       <c r="G24" s="2"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:17" ht="17.25" thickBot="1">
+    <row r="25" spans="1:17" ht="18" thickBot="1">
       <c r="A25" s="11"/>
       <c r="B25" s="16"/>
       <c r="C25" s="6"/>
@@ -1944,7 +1951,7 @@
       <c r="G25" s="2"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:17" ht="17.25" thickBot="1">
+    <row r="26" spans="1:17" ht="18" thickBot="1">
       <c r="A26" s="12"/>
       <c r="B26" s="17"/>
       <c r="C26" s="6"/>
@@ -1952,7 +1959,7 @@
       <c r="G26" s="2"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:17" ht="17.25" thickBot="1">
+    <row r="27" spans="1:17" ht="18" thickBot="1">
       <c r="A27" s="11"/>
       <c r="B27" s="16"/>
       <c r="C27" s="6"/>
@@ -1960,7 +1967,7 @@
       <c r="G27" s="2"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:17" ht="17.25" thickBot="1">
+    <row r="28" spans="1:17" ht="18" thickBot="1">
       <c r="A28" s="12"/>
       <c r="B28" s="17"/>
       <c r="C28" s="6"/>
@@ -1968,7 +1975,7 @@
       <c r="G28" s="2"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:17" ht="18" thickTop="1" thickBot="1">
+    <row r="29" spans="1:17" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A29" s="11"/>
       <c r="B29" s="16"/>
       <c r="C29" s="8"/>
@@ -1976,7 +1983,7 @@
       <c r="G29" s="2"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:17" ht="17.25" thickBot="1">
+    <row r="30" spans="1:17" ht="18" thickBot="1">
       <c r="A30" s="12"/>
       <c r="B30" s="17"/>
       <c r="C30" s="6"/>
@@ -1984,7 +1991,7 @@
       <c r="G30" s="2"/>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" spans="1:17" ht="17.25" thickBot="1">
+    <row r="31" spans="1:17" ht="18" thickBot="1">
       <c r="A31" s="11"/>
       <c r="B31" s="16"/>
       <c r="C31" s="6"/>
@@ -1992,7 +1999,7 @@
       <c r="G31" s="2"/>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" spans="1:17" ht="17.25" thickBot="1">
+    <row r="32" spans="1:17" ht="18" thickBot="1">
       <c r="A32" s="12"/>
       <c r="B32" s="17"/>
       <c r="C32" s="6"/>
@@ -2000,7 +2007,7 @@
       <c r="G32" s="2"/>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" spans="1:11" ht="17.25" thickBot="1">
+    <row r="33" spans="1:11" ht="18" thickBot="1">
       <c r="A33" s="11"/>
       <c r="B33" s="16"/>
       <c r="C33" s="6"/>
@@ -2008,7 +2015,7 @@
       <c r="G33" s="2"/>
       <c r="K33" s="4"/>
     </row>
-    <row r="34" spans="1:11" ht="17.25" thickBot="1">
+    <row r="34" spans="1:11" ht="18" thickBot="1">
       <c r="A34" s="12"/>
       <c r="B34" s="17"/>
       <c r="C34" s="6"/>
@@ -2016,7 +2023,7 @@
       <c r="G34" s="2"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="1:11" ht="17.25" thickBot="1">
+    <row r="35" spans="1:11" ht="18" thickBot="1">
       <c r="A35" s="11"/>
       <c r="B35" s="16"/>
       <c r="C35" s="6"/>
@@ -2024,7 +2031,7 @@
       <c r="G35" s="2"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:11" ht="17.25" thickBot="1">
+    <row r="36" spans="1:11" ht="18" thickBot="1">
       <c r="A36" s="12"/>
       <c r="B36" s="17"/>
       <c r="C36" s="7"/>
@@ -2032,7 +2039,7 @@
       <c r="G36" s="2"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:11" ht="17.25" thickBot="1">
+    <row r="37" spans="1:11" ht="18" thickBot="1">
       <c r="A37" s="11"/>
       <c r="B37" s="16"/>
       <c r="C37" s="6"/>
@@ -2040,7 +2047,7 @@
       <c r="G37" s="2"/>
       <c r="K37" s="4"/>
     </row>
-    <row r="38" spans="1:11" ht="17.25" thickBot="1">
+    <row r="38" spans="1:11" ht="18" thickBot="1">
       <c r="A38" s="4"/>
       <c r="B38" s="9"/>
       <c r="C38" s="6"/>
@@ -2048,7 +2055,7 @@
       <c r="G38" s="2"/>
       <c r="K38" s="4"/>
     </row>
-    <row r="39" spans="1:11" ht="17.25" thickBot="1">
+    <row r="39" spans="1:11" ht="18" thickBot="1">
       <c r="A39" s="4"/>
       <c r="B39" s="9"/>
       <c r="C39" s="6"/>
@@ -2056,7 +2063,7 @@
       <c r="G39" s="2"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:11" ht="17.25" thickBot="1">
+    <row r="40" spans="1:11" ht="18" thickBot="1">
       <c r="A40" s="4"/>
       <c r="B40" s="9"/>
       <c r="C40" s="6"/>
@@ -2064,7 +2071,7 @@
       <c r="G40" s="2"/>
       <c r="K40" s="4"/>
     </row>
-    <row r="41" spans="1:11" ht="17.25" thickBot="1">
+    <row r="41" spans="1:11" ht="18" thickBot="1">
       <c r="A41" s="4"/>
       <c r="B41" s="9"/>
       <c r="C41" s="6"/>
@@ -2072,7 +2079,7 @@
       <c r="G41" s="2"/>
       <c r="K41" s="4"/>
     </row>
-    <row r="42" spans="1:11" ht="17.25" thickBot="1">
+    <row r="42" spans="1:11" ht="18" thickBot="1">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
       <c r="C42" s="6"/>
@@ -2080,7 +2087,7 @@
       <c r="G42" s="2"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="1:11" ht="18" thickTop="1" thickBot="1">
+    <row r="43" spans="1:11" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
       <c r="C43" s="8"/>
@@ -2088,7 +2095,7 @@
       <c r="G43" s="2"/>
       <c r="K43" s="4"/>
     </row>
-    <row r="44" spans="1:11" ht="17.25" thickBot="1">
+    <row r="44" spans="1:11" ht="18" thickBot="1">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
       <c r="C44" s="6"/>
@@ -2096,7 +2103,7 @@
       <c r="G44" s="2"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45" spans="1:11" ht="17.25" thickBot="1">
+    <row r="45" spans="1:11" ht="18" thickBot="1">
       <c r="A45" s="4"/>
       <c r="B45" s="9"/>
       <c r="C45" s="6"/>
@@ -2104,7 +2111,7 @@
       <c r="G45" s="2"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="1:11" ht="17.25" thickBot="1">
+    <row r="46" spans="1:11" ht="18" thickBot="1">
       <c r="A46" s="4"/>
       <c r="B46" s="9"/>
       <c r="C46" s="6"/>
@@ -2112,7 +2119,7 @@
       <c r="G46" s="2"/>
       <c r="K46" s="4"/>
     </row>
-    <row r="47" spans="1:11" ht="17.25" thickBot="1">
+    <row r="47" spans="1:11" ht="18" thickBot="1">
       <c r="A47" s="4"/>
       <c r="B47" s="9"/>
       <c r="C47" s="6"/>
@@ -2120,22 +2127,22 @@
       <c r="G47" s="2"/>
       <c r="K47" s="4"/>
     </row>
-    <row r="48" spans="1:11" ht="17.25" thickBot="1">
+    <row r="48" spans="1:11" ht="18" thickBot="1">
       <c r="C48" s="6"/>
     </row>
-    <row r="49" spans="3:3" ht="17.25" thickBot="1">
+    <row r="49" spans="3:3" ht="18" thickBot="1">
       <c r="C49" s="6"/>
     </row>
-    <row r="50" spans="3:3" ht="17.25" thickBot="1">
+    <row r="50" spans="3:3" ht="18" thickBot="1">
       <c r="C50" s="7"/>
     </row>
-    <row r="51" spans="3:3" ht="18" thickTop="1" thickBot="1">
+    <row r="51" spans="3:3" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="C51" s="6"/>
     </row>
-    <row r="52" spans="3:3" ht="17.25" thickBot="1">
+    <row r="52" spans="3:3" ht="18" thickBot="1">
       <c r="C52" s="6"/>
     </row>
-    <row r="53" spans="3:3" ht="17.25" thickBot="1">
+    <row r="53" spans="3:3" ht="18" thickBot="1">
       <c r="C53" s="6"/>
     </row>
   </sheetData>
@@ -2155,7 +2162,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBA0246-B961-4C43-83D8-E960CF2453EE}">
   <dimension ref="A1:B70"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
   </cols>
@@ -2582,7 +2589,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{677ADA0E-C988-422F-B5F6-5CF6B4D028AF}">
   <dimension ref="A1:B70"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
   </cols>
@@ -2973,7 +2980,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0500CDB6-F6D5-4458-8137-AF5312222B51}">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="8" width="9" style="2"/>
   </cols>
@@ -3016,12 +3023,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17.25" thickBot="1">
+    <row r="8" spans="1:7" ht="18" thickBot="1">
       <c r="A8" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="9" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A9" s="19" t="s">
         <v>24</v>
       </c>
@@ -3044,7 +3051,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="10" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A10" s="19" t="s">
         <v>25</v>
       </c>
@@ -3067,7 +3074,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="11" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -3090,7 +3097,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="12" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -3128,12 +3135,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="17.25" thickBot="1">
+    <row r="16" spans="1:7" ht="18" thickBot="1">
       <c r="A16" s="19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="17" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A17" s="19" t="s">
         <v>32</v>
       </c>
@@ -3156,7 +3163,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="18" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A18" s="19" t="s">
         <v>33</v>
       </c>
@@ -3179,7 +3186,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="19" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A19" s="19" t="s">
         <v>56</v>
       </c>
@@ -3202,7 +3209,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="20" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A20" s="19" t="s">
         <v>57</v>
       </c>
@@ -3225,7 +3232,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="21" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A21" s="19" t="s">
         <v>58</v>
       </c>
@@ -3263,12 +3270,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="17.25" thickBot="1">
+    <row r="25" spans="1:8" ht="18" thickBot="1">
       <c r="A25" s="19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="26" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A26" s="19" t="s">
         <v>63</v>
       </c>
@@ -3291,7 +3298,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="27" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A27" s="19" t="s">
         <v>64</v>
       </c>
@@ -3314,7 +3321,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="28" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A28" s="19" t="s">
         <v>65</v>
       </c>
@@ -3340,7 +3347,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="29" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A29" s="19" t="s">
         <v>66</v>
       </c>
@@ -3366,7 +3373,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18" thickTop="1" thickBot="1">
+    <row r="30" spans="1:8" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A30" s="19" t="s">
         <v>67</v>
       </c>
@@ -3412,12 +3419,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="17.25" thickBot="1">
+    <row r="35" spans="1:7" ht="18" thickBot="1">
       <c r="A35" s="19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="36" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A36" s="19" t="s">
         <v>34</v>
       </c>
@@ -3470,12 +3477,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="17.25" thickBot="1">
+    <row r="43" spans="1:7" ht="18" thickBot="1">
       <c r="A43" s="19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="17.25" thickBot="1">
+    <row r="44" spans="1:7" ht="18" thickBot="1">
       <c r="A44" s="19" t="s">
         <v>41</v>
       </c>
@@ -3495,7 +3502,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="45" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A45" s="19" t="s">
         <v>42</v>
       </c>
@@ -3518,7 +3525,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="46" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A46" s="19" t="s">
         <v>43</v>
       </c>
@@ -3541,7 +3548,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="47" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A47" s="19" t="s">
         <v>44</v>
       </c>
@@ -3589,7 +3596,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="17.25" thickBot="1">
+    <row r="53" spans="1:7" ht="18" thickBot="1">
       <c r="A53" s="19" t="s">
         <v>50</v>
       </c>
@@ -3597,7 +3604,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="54" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A54" s="19" t="s">
         <v>73</v>
       </c>
@@ -3620,7 +3627,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="55" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A55" s="19" t="s">
         <v>74</v>
       </c>
@@ -3643,7 +3650,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="56" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A56" s="19" t="s">
         <v>75</v>
       </c>
@@ -3666,7 +3673,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="57" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A57" s="19" t="s">
         <v>76</v>
       </c>
@@ -3689,7 +3696,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="58" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A58" s="19" t="s">
         <v>77</v>
       </c>
@@ -3719,12 +3726,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="17.25" thickBot="1">
+    <row r="61" spans="1:7" ht="18" thickBot="1">
       <c r="A61" s="19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="17.25" thickBot="1">
+    <row r="62" spans="1:7" ht="18" thickBot="1">
       <c r="A62" s="19" t="s">
         <v>81</v>
       </c>
@@ -3744,7 +3751,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="63" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A63" s="19" t="s">
         <v>82</v>
       </c>
@@ -3767,7 +3774,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="64" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A64" s="19" t="s">
         <v>83</v>
       </c>
@@ -3790,7 +3797,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="65" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A65" s="19" t="s">
         <v>84</v>
       </c>
@@ -3813,7 +3820,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="18" thickTop="1" thickBot="1">
+    <row r="66" spans="1:7" ht="18.600000000000001" thickTop="1" thickBot="1">
       <c r="A66" s="19" t="s">
         <v>85</v>
       </c>
